--- a/TestData/TMTT0012113_ValidateCoExistFieldForGCATracking.xlsx
+++ b/TestData/TMTT0012113_ValidateCoExistFieldForGCATracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39CF52C-6F69-4558-8CB0-604350A4193A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF49373-E02A-4AAB-B292-E8AD115B82FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{6914B0A7-23C8-4C59-8A71-D12BF5352AB3}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{6914B0A7-23C8-4C59-8A71-D12BF5352AB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="ModuleName" sheetId="5" r:id="rId3"/>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId4"/>
     <sheet name="AddContact" sheetId="2" r:id="rId5"/>
-    <sheet name="InternalTeam" sheetId="6" r:id="rId6"/>
+    <sheet name="OppDealTeamMembers" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="91">
   <si>
     <t>Client</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Activism Advisory</t>
+  </si>
+  <si>
+    <t>Analyst</t>
   </si>
 </sst>
 </file>
@@ -354,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -362,7 +365,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -698,14 +700,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533E536B-B7DF-4CA3-886D-7CBD31363DCD}">
   <dimension ref="A1:AB4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
@@ -716,7 +718,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -733,7 +735,7 @@
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -744,7 +746,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -763,14 +765,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DA9484C-3321-40A2-8DBC-82467259E8DC}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -783,22 +785,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B4AA16-114A-488D-B988-48E1BF5E1B86}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -811,36 +813,36 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28710558-C34E-4463-B41D-5BFD4F346D1C}">
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="27" max="27" width="11.44140625" customWidth="1"/>
-    <col min="29" max="29" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" customWidth="1"/>
+    <col min="29" max="29" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -935,7 +937,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -1030,14 +1032,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>89</v>
       </c>
       <c r="D3" t="s">
@@ -1133,17 +1135,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{935637E3-2FF3-414E-8DF7-082775A8C6A6}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>55</v>
       </c>
@@ -1169,7 +1171,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -1202,34 +1204,44 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50423EC6-F997-4E60-A436-3E9753BC8546}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
       <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>86</v>
       </c>
       <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
         <v>87</v>
       </c>
     </row>

--- a/TestData/TMTT0012113_ValidateCoExistFieldForGCATracking.xlsx
+++ b/TestData/TMTT0012113_ValidateCoExistFieldForGCATracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF49373-E02A-4AAB-B292-E8AD115B82FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBB9FE8-15E6-477D-978A-B8CECE2084C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{6914B0A7-23C8-4C59-8A71-D12BF5352AB3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6914B0A7-23C8-4C59-8A71-D12BF5352AB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>Client</t>
   </si>
@@ -139,9 +139,6 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -160,9 +157,6 @@
     <t>Do Not Disclose</t>
   </si>
   <si>
-    <t>Rob Oudman</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -202,9 +196,6 @@
     <t>Debtor Advisors</t>
   </si>
   <si>
-    <t>Ayati Arvind</t>
-  </si>
-  <si>
     <t>FR</t>
   </si>
   <si>
@@ -314,6 +305,18 @@
   </si>
   <si>
     <t>Analyst</t>
+  </si>
+  <si>
+    <t>FA - Portfolio-Auto Loans</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>FVA</t>
+  </si>
+  <si>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -345,7 +348,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -353,11 +356,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -365,6 +383,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -709,24 +728,24 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -737,24 +756,24 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -769,12 +788,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -792,17 +811,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +831,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28710558-C34E-4463-B41D-5BFD4F346D1C}">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -945,91 +964,91 @@
         <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="N2" t="s">
-        <v>53</v>
-      </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>41</v>
       </c>
-      <c r="S2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="V2" t="s">
         <v>42</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>43</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z2" t="s">
         <v>46</v>
       </c>
-      <c r="Y2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC2" t="s">
         <v>48</v>
       </c>
-      <c r="AA2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>34</v>
-      </c>
       <c r="AD2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AE2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -1040,91 +1059,186 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
         <v>89</v>
       </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="L4" t="s">
         <v>36</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M4" t="s">
         <v>37</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N4" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="S4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="U4" t="s">
         <v>41</v>
       </c>
-      <c r="S3" t="s">
-        <v>41</v>
-      </c>
-      <c r="T3" s="3" t="s">
+      <c r="V4" t="s">
         <v>42</v>
       </c>
-      <c r="U3" t="s">
+      <c r="W4" t="s">
         <v>43</v>
       </c>
-      <c r="V3" t="s">
+      <c r="X4" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="Y4" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z4" t="s">
         <v>46</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AB4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC4" t="s">
         <v>48</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AD4" t="s">
         <v>49</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AE4" t="s">
         <v>49</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1147,54 +1261,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1214,35 +1328,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
         <v>82</v>
-      </c>
-      <c r="B2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0012113_ValidateCoExistFieldForGCATracking.xlsx
+++ b/TestData/TMTT0012113_ValidateCoExistFieldForGCATracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823AB8E8-895E-414A-88FF-AE18B3E42327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694AC7BA-6ADE-40DC-A2AA-F0146E11D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6914B0A7-23C8-4C59-8A71-D12BF5352AB3}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{6914B0A7-23C8-4C59-8A71-D12BF5352AB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="3" r:id="rId1"/>
@@ -256,9 +256,6 @@
     <t>Dimitri Drone</t>
   </si>
   <si>
-    <t>Liz Hedgcock</t>
-  </si>
-  <si>
     <t>Eric Winthrop</t>
   </si>
   <si>
@@ -320,6 +317,9 @@
   </si>
   <si>
     <t>LOB</t>
+  </si>
+  <si>
+    <t>Blaise Brunda</t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533E536B-B7DF-4CA3-886D-7CBD31363DCD}">
   <dimension ref="A1:AC4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>65</v>
@@ -743,18 +743,18 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
         <v>72</v>
       </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
@@ -763,7 +763,7 @@
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -774,21 +774,21 @@
         <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -799,16 +799,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DA9484C-3321-40A2-8DBC-82467259E8DC}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -819,24 +819,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B4AA16-114A-488D-B988-48E1BF5E1B86}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -847,36 +847,36 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28710558-C34E-4463-B41D-5BFD4F346D1C}">
   <dimension ref="A1:AE4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="27" max="27" width="11.44140625" customWidth="1"/>
-    <col min="29" max="29" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" customWidth="1"/>
+    <col min="29" max="29" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -971,7 +971,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -982,7 +982,7 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -1012,7 +1012,7 @@
         <v>37</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>38</v>
@@ -1066,7 +1066,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1074,10 +1074,10 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>32</v>
@@ -1161,7 +1161,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1169,10 +1169,10 @@
         <v>31</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>32</v>
@@ -1193,7 +1193,7 @@
         <v>33</v>
       </c>
       <c r="K4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
@@ -1235,7 +1235,7 @@
         <v>44</v>
       </c>
       <c r="Y4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Z4" t="s">
         <v>46</v>
@@ -1264,17 +1264,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{935637E3-2FF3-414E-8DF7-082775A8C6A6}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -1334,44 +1334,44 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50423EC6-F997-4E60-A436-3E9753BC8546}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
         <v>83</v>
-      </c>
-      <c r="B3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0012113_ValidateCoExistFieldForGCATracking.xlsx
+++ b/TestData/TMTT0012113_ValidateCoExistFieldForGCATracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694AC7BA-6ADE-40DC-A2AA-F0146E11D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3556C0C-2567-44C9-B301-1678BB4F2110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{6914B0A7-23C8-4C59-8A71-D12BF5352AB3}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="27000" windowHeight="14115" xr2:uid="{6914B0A7-23C8-4C59-8A71-D12BF5352AB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="3" r:id="rId1"/>
@@ -250,9 +250,6 @@
     <t>James Craven</t>
   </si>
   <si>
-    <t>Gemma Hardy</t>
-  </si>
-  <si>
     <t>Dimitri Drone</t>
   </si>
   <si>
@@ -320,6 +317,9 @@
   </si>
   <si>
     <t>Blaise Brunda</t>
+  </si>
+  <si>
+    <t>Jennie Stewart</t>
   </si>
 </sst>
 </file>
@@ -731,7 +731,7 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>65</v>
@@ -748,13 +748,13 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
@@ -771,24 +771,24 @@
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -803,12 +803,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -826,17 +826,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -982,7 +982,7 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -1012,7 +1012,7 @@
         <v>37</v>
       </c>
       <c r="N2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>38</v>
@@ -1074,10 +1074,10 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>32</v>
@@ -1169,10 +1169,10 @@
         <v>31</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>32</v>
@@ -1193,7 +1193,7 @@
         <v>33</v>
       </c>
       <c r="K4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
@@ -1202,7 +1202,7 @@
         <v>37</v>
       </c>
       <c r="N4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>38</v>
@@ -1235,7 +1235,7 @@
         <v>44</v>
       </c>
       <c r="Y4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z4" t="s">
         <v>46</v>
@@ -1343,35 +1343,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
         <v>82</v>
-      </c>
-      <c r="B3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0012113_ValidateCoExistFieldForGCATracking.xlsx
+++ b/TestData/TMTT0012113_ValidateCoExistFieldForGCATracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3556C0C-2567-44C9-B301-1678BB4F2110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C81778-EB78-4B6D-B3F9-7316AF7403E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="27000" windowHeight="14115" xr2:uid="{6914B0A7-23C8-4C59-8A71-D12BF5352AB3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{6914B0A7-23C8-4C59-8A71-D12BF5352AB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="3" r:id="rId1"/>
